--- a/output/pdf_financials_xlsx/RCT.xlsx
+++ b/output/pdf_financials_xlsx/RCT.xlsx
@@ -6077,52 +6077,52 @@
         <v>4.805497</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>6.957287</v>
+        <v>6.933133</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>6.977012</v>
+        <v>6.951073</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>6.951073</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>7.228173</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.471472</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.471472</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.471472</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.471472</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.471472</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.471472</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.471472</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.537022</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.537022</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.537022</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.537022</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0.243299</v>
+        <v>7.631302</v>
       </c>
     </row>
     <row r="93">
@@ -10707,7 +10707,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -15141,7 +15145,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -16974,7 +16982,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>
@@ -18148,7 +18160,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RCT.xlsx
+++ b/output/pdf_financials_xlsx/RCT.xlsx
@@ -1124,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.013984</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002297</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -2254,10 +2254,10 @@
         <v>-0.057686</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.151169</v>
+        <v>-1.165153</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-9.695288</v>
+        <v>-9.697585</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-13.045681</v>
@@ -2390,10 +2390,10 @@
         <v>-0.057686</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.151169</v>
+        <v>-1.165153</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-9.695288</v>
+        <v>-9.697585</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-13.045681</v>
@@ -2458,10 +2458,10 @@
         <v>-0.4616599221550106</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-8.658763401718996</v>
+        <v>-8.763947043225707</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-90.50922083724564</v>
+        <v>-90.53066421058979</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-176.2222356402585</v>
@@ -2654,55 +2654,55 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.154082</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>3.643382</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.28338</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.272352</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.085107</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.019639</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.020536</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.024854</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.023692</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.03587</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.00629</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.322876</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.668534</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.347045</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.18152</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.119951</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.099217</v>
       </c>
     </row>
     <row r="35">
@@ -2770,55 +2770,55 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.154082</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>3.643382</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.28338</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.272352</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.085107</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.019639</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.020536</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.024854</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.023692</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.03587</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.00629</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.322876</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.668534</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.347045</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.18152</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.119951</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.099217</v>
       </c>
     </row>
     <row r="37">
@@ -3466,55 +3466,55 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.506258</v>
+        <v>0.352176</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.695123</v>
+        <v>0.051741</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.337879</v>
+        <v>0.054499</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.428064</v>
+        <v>0.155712</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.318271</v>
+        <v>0.233164</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.42786</v>
+        <v>0.408221</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.76215</v>
+        <v>0.741614</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.737432</v>
+        <v>0.712578</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.661252</v>
+        <v>0.63756</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.765061</v>
+        <v>0.729191</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.339628</v>
+        <v>0.333338</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.643572</v>
+        <v>0.320696</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>1.167953</v>
+        <v>0.499419</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>1.104256</v>
+        <v>0.757211</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.197553</v>
+        <v>1.016033</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>1.554265</v>
+        <v>1.434314</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>1.876812</v>
+        <v>1.777595</v>
       </c>
     </row>
     <row r="49">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -22092,7 +22092,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E141" s="5" t="n">
@@ -28888,7 +28888,11 @@
           <t>Repayment of indebtedness</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -37826,7 +37830,7 @@
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
@@ -40060,7 +40064,7 @@
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">

--- a/output/pdf_financials_xlsx/RCT.xlsx
+++ b/output/pdf_financials_xlsx/RCT.xlsx
@@ -1381,13 +1381,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>-10.946061</v>
+        <v>-9.106061</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>-9.641083999999999</v>
+        <v>-7.443584</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-11.372488</v>
+        <v>-11.311228</v>
       </c>
       <c r="E16" s="3" t="n">
         <v>2.417785</v>
@@ -1449,13 +1449,13 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.84</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0</v>
+        <v>-2.1975</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.06126</v>
       </c>
       <c r="E17" s="3" t="n">
         <v>-0</v>
@@ -2239,13 +2239,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-10.946061</v>
+        <v>-9.106061</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-9.641083999999999</v>
+        <v>-7.443584</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.372488</v>
+        <v>-11.311228</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>2.417785</v>
@@ -2375,13 +2375,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-10.946061</v>
+        <v>-9.106061</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-9.641083999999999</v>
+        <v>-7.443584</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.372488</v>
+        <v>-11.311228</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>2.417785</v>
@@ -2443,13 +2443,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-279.9831335785282</v>
+        <v>-232.9188091805104</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-115.2675784215617</v>
+        <v>-88.99454692620476</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-123.661327340605</v>
+        <v>-122.9952028379557</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>20.78080191977364</v>
@@ -2511,13 +2511,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>-0</v>
+        <v>-20.20632192119073</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-0</v>
+        <v>-29.52206893883377</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-0.5415857588583662</v>
       </c>
       <c r="E31" s="3" t="n">
         <v>0</v>
@@ -32589,7 +32589,11 @@
           <t>Future income tax recovery</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E250" s="5" t="n">
         <v>-1.84</v>
       </c>
@@ -42888,7 +42892,11 @@
           <t>FUTURE INCOME TAX RECOVERY (Note 15)</t>
         </is>
       </c>
-      <c r="D353" t="inlineStr"/>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E353" s="5" t="n">
         <v>1.84</v>
       </c>
